--- a/export from sqliteonline.com (1).xlsx
+++ b/export from sqliteonline.com (1).xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8BB698E1878D22D7A99FA500AB808E73916DA1D8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Page 1" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="SQL" state="visible" r:id="rId5"/>
+    <sheet name="Page 1" sheetId="1" r:id="rId1"/>
+    <sheet name="SQL" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -515,7 +519,7 @@
     <t>Page 1</t>
   </si>
   <si>
-    <t xml:space="preserve">WITH attendance AS
+    <t>WITH attendance AS
 (
     SELECT
         date,
@@ -596,17 +600,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -972,11 +978,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -993,7 +999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1010,7 +1016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1027,7 +1033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1078,7 +1084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1095,7 +1101,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1112,7 +1118,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1163,7 +1169,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1197,7 +1203,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1231,7 +1237,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1248,7 +1254,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -1265,7 +1271,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1282,7 +1288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -1299,7 +1305,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1350,7 +1356,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -1367,7 +1373,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -1384,7 +1390,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -1418,7 +1424,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>87</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -1452,7 +1458,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -1469,7 +1475,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>95</v>
       </c>
@@ -1486,7 +1492,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>102</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -1537,7 +1543,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -1554,7 +1560,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>111</v>
       </c>
@@ -1571,7 +1577,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -1605,7 +1611,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>123</v>
       </c>
@@ -1622,7 +1628,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>127</v>
       </c>
@@ -1639,7 +1645,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -1656,7 +1662,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -1673,7 +1679,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>134</v>
       </c>
@@ -1690,7 +1696,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -1707,7 +1713,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -1724,7 +1730,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -1741,7 +1747,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>152</v>
       </c>
@@ -1758,7 +1764,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>156</v>
       </c>
@@ -1775,7 +1781,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>156</v>
       </c>
@@ -1792,7 +1798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>162</v>
       </c>
@@ -1811,16 +1817,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>166</v>
       </c>
@@ -1830,6 +1836,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>